--- a/data/露天.xlsx
+++ b/data/露天.xlsx
@@ -1,43 +1,257 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pythonworkspace\e-commerce-ERP-system-streamlit-app\data_dev\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88D3751-49D3-473F-A878-925CE265BEA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="67">
+  <si>
+    <t>結帳時間</t>
+  </si>
+  <si>
+    <t>訂單編號</t>
+  </si>
+  <si>
+    <t>訂單狀態</t>
+  </si>
+  <si>
+    <t>付款方式</t>
+  </si>
+  <si>
+    <t>付款時間</t>
+  </si>
+  <si>
+    <t>買家帳號</t>
+  </si>
+  <si>
+    <t>商品編號</t>
+  </si>
+  <si>
+    <t>商品名稱</t>
+  </si>
+  <si>
+    <t>規格</t>
+  </si>
+  <si>
+    <t>項目</t>
+  </si>
+  <si>
+    <t>賣家自用料號</t>
+  </si>
+  <si>
+    <t>數量</t>
+  </si>
+  <si>
+    <t>單價</t>
+  </si>
+  <si>
+    <t>運送方式</t>
+  </si>
+  <si>
+    <t>露天折扣碼金額</t>
+  </si>
+  <si>
+    <t>賣家折扣碼金額</t>
+  </si>
+  <si>
+    <t>運費</t>
+  </si>
+  <si>
+    <t>露幣折抵金額</t>
+  </si>
+  <si>
+    <t>結帳總金額</t>
+  </si>
+  <si>
+    <t>給賣家的話</t>
+  </si>
+  <si>
+    <t>交易狀況</t>
+  </si>
+  <si>
+    <t>物流追蹤碼/交貨便代碼/寄件代碼/郵局配送單號</t>
+  </si>
+  <si>
+    <t>收件人姓名</t>
+  </si>
+  <si>
+    <t>電話</t>
+  </si>
+  <si>
+    <t>手機</t>
+  </si>
+  <si>
+    <t>收件地址</t>
+  </si>
+  <si>
+    <t>2026/02/09</t>
+  </si>
+  <si>
+    <t>26020946668756</t>
+  </si>
+  <si>
+    <t>已出貨</t>
+  </si>
+  <si>
+    <t>7-11取貨付款</t>
+  </si>
+  <si>
+    <t>post004100</t>
+  </si>
+  <si>
+    <t>21828333346889</t>
+  </si>
+  <si>
+    <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+  </si>
+  <si>
+    <t>寶藍色</t>
+  </si>
+  <si>
+    <t>L ➜建議70-75KG</t>
+  </si>
+  <si>
+    <t>HME03001-PB-L</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+  </si>
+  <si>
+    <t>N59688810691</t>
+  </si>
+  <si>
+    <t>鄧*誌</t>
+  </si>
+  <si>
+    <t>0930******</t>
+  </si>
+  <si>
+    <t>萬應門市||高雄市苓雅區四維四路190-1號||N||0</t>
+  </si>
+  <si>
+    <t>藏藍色</t>
+  </si>
+  <si>
+    <t>HME03001-DN-L</t>
+  </si>
+  <si>
+    <t>黑色</t>
+  </si>
+  <si>
+    <t>HME03001-BK-L</t>
+  </si>
+  <si>
+    <t>白色</t>
+  </si>
+  <si>
+    <t>2026/02/03</t>
+  </si>
+  <si>
+    <t>26020345883124</t>
+  </si>
+  <si>
+    <t>kuzzar</t>
+  </si>
+  <si>
+    <t>22447281456959</t>
+  </si>
+  <si>
+    <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE</t>
+  </si>
+  <si>
+    <t>白色｜高領</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>HFA02001-WH_TN-L</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
+    <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+  </si>
+  <si>
+    <t>N33024165187</t>
+  </si>
+  <si>
+    <t>楊*賓</t>
+  </si>
+  <si>
+    <t>**********</t>
+  </si>
+  <si>
+    <t>白色｜圓領</t>
+  </si>
+  <si>
+    <t>HFA02001-WH_CN-L</t>
+  </si>
+  <si>
+    <t>22031995614204</t>
+  </si>
+  <si>
+    <t>超舒適零觸感❄夏季涼爽高彈力純棉中腰無痕冰絲三角褲｜高彈力材料｜通過SGS認證｜內褲｜三角內褲｜女士內褲｜台灣現貨</t>
+  </si>
+  <si>
+    <t>HFE03001-WH-L</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,101 +259,33 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -177,7 +323,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -211,6 +357,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -245,9 +392,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -420,147 +568,527 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Z1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Z7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>結帳時間</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>訂單編號</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>訂單狀態</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>付款方式</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>付款時間</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>買家帳號</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>商品編號</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>商品名稱</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>規格</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>賣家自用料號</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>數量</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>單價</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>運送方式</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>露天折扣碼金額</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>賣家折扣碼金額</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>運費</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>露幣折抵金額</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>結帳總金額</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>給賣家的話</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>交易狀況</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>物流追蹤碼/交貨便代碼/寄件代碼/郵局配送單號</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>收件人姓名</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>電話</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>手機</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>收件地址</t>
-        </is>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>65</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>400</v>
+      </c>
+      <c r="U2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V2" t="s">
+        <v>39</v>
+      </c>
+      <c r="W2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>65</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>400</v>
+      </c>
+      <c r="U3" t="s">
+        <v>38</v>
+      </c>
+      <c r="V3" t="s">
+        <v>39</v>
+      </c>
+      <c r="W3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>65</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>400</v>
+      </c>
+      <c r="U4" t="s">
+        <v>38</v>
+      </c>
+      <c r="V4" t="s">
+        <v>39</v>
+      </c>
+      <c r="W4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" t="s">
+        <v>54</v>
+      </c>
+      <c r="K5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L5" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" t="s">
+        <v>56</v>
+      </c>
+      <c r="N5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>352</v>
+      </c>
+      <c r="U5" t="s">
+        <v>57</v>
+      </c>
+      <c r="V5" t="s">
+        <v>58</v>
+      </c>
+      <c r="W5" t="s">
+        <v>59</v>
+      </c>
+      <c r="X5" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J6" t="s">
+        <v>54</v>
+      </c>
+      <c r="K6" t="s">
+        <v>62</v>
+      </c>
+      <c r="L6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M6" t="s">
+        <v>56</v>
+      </c>
+      <c r="N6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>352</v>
+      </c>
+      <c r="U6" t="s">
+        <v>57</v>
+      </c>
+      <c r="V6" t="s">
+        <v>58</v>
+      </c>
+      <c r="W6" t="s">
+        <v>59</v>
+      </c>
+      <c r="X6" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H7" t="s">
+        <v>64</v>
+      </c>
+      <c r="I7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K7" t="s">
+        <v>65</v>
+      </c>
+      <c r="L7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M7" t="s">
+        <v>66</v>
+      </c>
+      <c r="N7" t="s">
+        <v>29</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>352</v>
+      </c>
+      <c r="U7" t="s">
+        <v>57</v>
+      </c>
+      <c r="V7" t="s">
+        <v>58</v>
+      </c>
+      <c r="W7" t="s">
+        <v>59</v>
+      </c>
+      <c r="X7" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/露天.xlsx
+++ b/data/露天.xlsx
@@ -1,134 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pythonworkspace\e-commerce-ERP-system-streamlit-app\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3224B3E-777E-4E9B-A419-F0C685A5FE25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
-  <si>
-    <t>結帳時間</t>
-  </si>
-  <si>
-    <t>訂單編號</t>
-  </si>
-  <si>
-    <t>訂單狀態</t>
-  </si>
-  <si>
-    <t>付款方式</t>
-  </si>
-  <si>
-    <t>付款時間</t>
-  </si>
-  <si>
-    <t>買家帳號</t>
-  </si>
-  <si>
-    <t>商品編號</t>
-  </si>
-  <si>
-    <t>商品名稱</t>
-  </si>
-  <si>
-    <t>規格</t>
-  </si>
-  <si>
-    <t>項目</t>
-  </si>
-  <si>
-    <t>賣家自用料號</t>
-  </si>
-  <si>
-    <t>數量</t>
-  </si>
-  <si>
-    <t>單價</t>
-  </si>
-  <si>
-    <t>運送方式</t>
-  </si>
-  <si>
-    <t>露天折扣碼金額</t>
-  </si>
-  <si>
-    <t>賣家折扣碼金額</t>
-  </si>
-  <si>
-    <t>運費</t>
-  </si>
-  <si>
-    <t>露幣折抵金額</t>
-  </si>
-  <si>
-    <t>結帳總金額</t>
-  </si>
-  <si>
-    <t>給賣家的話</t>
-  </si>
-  <si>
-    <t>交易狀況</t>
-  </si>
-  <si>
-    <t>物流追蹤碼/交貨便代碼/寄件代碼/郵局配送單號</t>
-  </si>
-  <si>
-    <t>收件人姓名</t>
-  </si>
-  <si>
-    <t>電話</t>
-  </si>
-  <si>
-    <t>手機</t>
-  </si>
-  <si>
-    <t>收件地址</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="3"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -136,33 +45,101 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -200,7 +177,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -234,7 +211,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -269,10 +245,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -445,92 +420,771 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>結帳時間</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>訂單編號</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>訂單狀態</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>付款方式</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>付款時間</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>買家帳號</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>商品編號</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>商品名稱</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>規格</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>賣家自用料號</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>數量</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>單價</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>運送方式</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>露天折扣碼金額</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>賣家折扣碼金額</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>運費</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>露幣折抵金額</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>結帳總金額</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>給賣家的話</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>交易狀況</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>物流追蹤碼/交貨便代碼/寄件代碼/郵局配送單號</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>收件人姓名</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>手機</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>收件地址</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>25</v>
+      <c r="M2" t="n">
+        <v>67</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>65</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>400</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0930******</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>萬應門市||高雄市苓雅區四維四路190-1號||N||0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>藏藍色</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>HME03001-DN-L</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>67</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>65</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>400</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0930******</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>萬應門市||高雄市苓雅區四維四路190-1號||N||0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>67</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>65</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>400</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0930******</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>萬應門市||高雄市苓雅區四維四路190-1號||N||0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>22447281456959</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>白色｜高領</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>HFA02001-WH_TN-L</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>155</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>352</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>22447281456959</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>白色｜圓領</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>HFA02001-WH_CN-L</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>155</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>352</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>22031995614204</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>超舒適零觸感❄夏季涼爽高彈力純棉中腰無痕冰絲三角褲｜高彈力材料｜通過SGS認證｜內褲｜三角內褲｜女士內褲｜台灣現貨</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>白色</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>HFE03001-WH-L</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>42</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>352</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/露天.xlsx
+++ b/data/露天.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,6 +557,630 @@
       <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>收件地址</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>67</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>65</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>400</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0930******</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>萬應門市||高雄市苓雅區四維四路190-1號||N||0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>藏藍色</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>HME03001-DN-L</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>67</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>65</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>400</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0930******</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>萬應門市||高雄市苓雅區四維四路190-1號||N||0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>67</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>65</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>400</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0930******</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>萬應門市||高雄市苓雅區四維四路190-1號||N||0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>22447281456959</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>白色｜高領</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>HFA02001-WH_TN-L</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>155</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>352</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>22447281456959</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>白色｜圓領</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>HFA02001-WH_CN-L</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>155</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>352</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>22031995614204</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>超舒適零觸感❄夏季涼爽高彈力純棉中腰無痕冰絲三角褲｜高彈力材料｜通過SGS認證｜內褲｜三角內褲｜女士內褲｜台灣現貨</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>白色</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>HFE03001-WH-L</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>42</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>352</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>**********</t>
         </is>
       </c>
     </row>

--- a/data/露天.xlsx
+++ b/data/露天.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,6 +557,1576 @@
       <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>收件地址</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>67</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>65</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>400</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0930******</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>萬應門市||高雄市苓雅區四維四路190-1號||N||0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>藏藍色</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>HME03001-DN-L</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>67</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>65</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>400</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0930******</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>萬應門市||高雄市苓雅區四維四路190-1號||N||0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>67</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>65</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>400</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0930******</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>萬應門市||高雄市苓雅區四維四路190-1號||N||0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>白色</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>HME03001-WH-L</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>67</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>65</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>400</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0930******</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>萬應門市||高雄市苓雅區四維四路190-1號||N||0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>咖啡色</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>HME03001-BR-L</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>67</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>65</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>400</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0930******</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>萬應門市||高雄市苓雅區四維四路190-1號||N||0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>HME03001-PB-XL</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>67</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>100</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>703</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>02/10通知已出貨&lt;br&gt;02/07 透過支付連&lt;span class='rt-text-danger'&gt;信用卡付款(一次付清)成功&lt;/span&gt;，款項將於 &lt;span class='rt-text-danger'&gt;03/04&lt;/span&gt; 或訂單完成後撥款給您</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0921014729</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>雲林縣 崙背鄉 枋南村16之10號</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>咖啡色</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>HME03001-BR-XL</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>67</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>100</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>703</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>02/10通知已出貨&lt;br&gt;02/07 透過支付連&lt;span class='rt-text-danger'&gt;信用卡付款(一次付清)成功&lt;/span&gt;，款項將於 &lt;span class='rt-text-danger'&gt;03/04&lt;/span&gt; 或訂單完成後撥款給您</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0921014729</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>雲林縣 崙背鄉 枋南村16之10號</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>酒紅色</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>HME03001-RD-XL</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>67</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>703</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>02/10通知已出貨&lt;br&gt;02/07 透過支付連&lt;span class='rt-text-danger'&gt;信用卡付款(一次付清)成功&lt;/span&gt;，款項將於 &lt;span class='rt-text-danger'&gt;03/04&lt;/span&gt; 或訂單完成後撥款給您</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0921014729</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>雲林縣 崙背鄉 枋南村16之10號</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>藏藍色</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>HME03001-DN-XL</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>67</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>100</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>703</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>02/10通知已出貨&lt;br&gt;02/07 透過支付連&lt;span class='rt-text-danger'&gt;信用卡付款(一次付清)成功&lt;/span&gt;，款項將於 &lt;span class='rt-text-danger'&gt;03/04&lt;/span&gt; 或訂單完成後撥款給您</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0921014729</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>雲林縣 崙背鄉 枋南村16之10號</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>紫色</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>HME03001-PU-XL</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>67</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>100</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>703</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>02/10通知已出貨&lt;br&gt;02/07 透過支付連&lt;span class='rt-text-danger'&gt;信用卡付款(一次付清)成功&lt;/span&gt;，款項將於 &lt;span class='rt-text-danger'&gt;03/04&lt;/span&gt; 或訂單完成後撥款給您</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0921014729</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>雲林縣 崙背鄉 枋南村16之10號</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>灰色</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>HME03001-GY-XL</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>67</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>100</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>703</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>02/10通知已出貨&lt;br&gt;02/07 透過支付連&lt;span class='rt-text-danger'&gt;信用卡付款(一次付清)成功&lt;/span&gt;，款項將於 &lt;span class='rt-text-danger'&gt;03/04&lt;/span&gt; 或訂單完成後撥款給您</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0921014729</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>雲林縣 崙背鄉 枋南村16之10號</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>白色</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>HME03001-WH-XL</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>67</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>100</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>703</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>02/10通知已出貨&lt;br&gt;02/07 透過支付連&lt;span class='rt-text-danger'&gt;信用卡付款(一次付清)成功&lt;/span&gt;，款項將於 &lt;span class='rt-text-danger'&gt;03/04&lt;/span&gt; 或訂單完成後撥款給您</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>0921014729</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>雲林縣 崙背鄉 枋南村16之10號</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>22447281456959</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>白色｜高領</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>HFA02001-WH_TN-L</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>155</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>352</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>22447281456959</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>白色｜圓領</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>HFA02001-WH_CN-L</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>155</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>352</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>22031995614204</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>超舒適零觸感❄夏季涼爽高彈力純棉中腰無痕冰絲三角褲｜高彈力材料｜通過SGS認證｜內褲｜三角內褲｜女士內褲｜台灣現貨</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>白色</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>HFE03001-WH-L</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>42</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>352</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>**********</t>
         </is>
       </c>
     </row>

--- a/data/露天.xlsx
+++ b/data/露天.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,142 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>結帳時間</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>訂單編號</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>訂單狀態</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>付款方式</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>付款時間</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>買家帳號</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>商品編號</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>商品名稱</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>規格</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>賣家自用料號</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>數量</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>單價</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>運送方式</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>露天折扣碼金額</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>賣家折扣碼金額</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>運費</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>露幣折抵金額</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>結帳總金額</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>給賣家的話</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>交易狀況</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>物流追蹤碼/交貨便代碼/寄件代碼/郵局配送單號</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>收件人姓名</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>電話</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>手機</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>收件地址</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/露天.xlsx
+++ b/data/露天.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,340 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:Z5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>結帳時間</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>訂單編號</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>訂單狀態</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>付款方式</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>付款時間</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>買家帳號</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>商品編號</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>商品名稱</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>規格</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>賣家自用料號</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>數量</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>單價</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>運送方式</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>露天折扣碼金額</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>賣家折扣碼金額</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>運費</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>露幣折抵金額</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>結帳總金額</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>給賣家的話</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>交易狀況</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>物流追蹤碼/交貨便代碼/寄件代碼/郵局配送單號</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>收件人姓名</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>手機</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>收件地址</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025/06/25</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>25062521046189</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>akk238</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>S ➜建議50-55KG</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>HME03001-BK-S</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>67</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>65</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>400</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2025/07/09&lt;br&gt;07/08 已領取退貨</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>E57180550168</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>高*華</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>買家未取貨，日報表需列出，未取貨/退貨運費 視該筆訂單（D_付款方式）選擇的超商方式計入費用；不扣庫存，不計入出庫</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>7-11取貨$60／全家取貨$60／OK超商取貨$60／萊爾富取貨$50／中華郵政$65（中華郵政部份是否能設定手KEY）</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/露天.xlsx
+++ b/data/露天.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,204 +559,6 @@
           <t>收件地址</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2025/06/25</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>25062521046189</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>已出貨</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>7-11取貨付款</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>akk238</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>21828333346889</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>黑色</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>S ➜建議50-55KG</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>HME03001-BK-S</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M2" t="n">
-        <v>67</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>7-11取貨付款</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>65</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>400</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>訂單完成&lt;br&gt;2025/07/09&lt;br&gt;07/08 已領取退貨</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>E57180550168</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>高*華</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>**********</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>**********</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>**********</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>買家未取貨，日報表需列出，未取貨/退貨運費 視該筆訂單（D_付款方式）選擇的超商方式計入費用；不扣庫存，不計入出庫</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>7-11取貨$60／全家取貨$60／OK超商取貨$60／萊爾富取貨$50／中華郵政$65（中華郵政部份是否能設定手KEY）</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/露天.xlsx
+++ b/data/露天.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,880 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>結帳時間</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>訂單編號</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>訂單狀態</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>付款方式</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>付款時間</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>買家帳號</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>商品編號</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>商品名稱</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>規格</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>賣家自用料號</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>數量</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>單價</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>運送方式</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>露天折扣碼金額</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>賣家折扣碼金額</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>運費</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>露幣折抵金額</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>結帳總金額</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>給賣家的話</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>交易狀況</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>物流追蹤碼/交貨便代碼/寄件代碼/郵局配送單號</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>收件人姓名</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>手機</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>收件地址</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026/01/20</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>26012044321148</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>jimshue</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>22212317280954</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>『單顆入』好評銷售冠軍👑台灣天然養生手工黑糖塊｜老薑紅棗桂圓海燕窩｜冬日暖身｜生理期保養｜暖男送女友必備🎁｜黑糖磚</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>老薑黑糖塊</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>YGJ03002-OG</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>17</v>
+      </c>
+      <c r="S2" t="n">
+        <v>83</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/01/26&lt;br&gt;01/24 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>26DME37477238</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>許*誠</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026/01/13</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>26011343534591</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>x200129</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>67</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1005</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/01/15&lt;br&gt;01/15 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>M51801615754</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>朱*慶</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026/01/13</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>26011343534591</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>x200129</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>咖啡色</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>HME03001-BR-L</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>67</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1005</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/01/15&lt;br&gt;01/15 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>M51801615754</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>朱*慶</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026/01/13</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>26011343534591</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>x200129</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>灰色</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>HME03001-GY-L</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>67</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1005</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/01/15&lt;br&gt;01/15 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>M51801615754</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>朱*慶</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026/01/13</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>26011343534591</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>x200129</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>酒紅色</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>HME03001-RD-L</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>67</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1005</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/01/15&lt;br&gt;01/15 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>M51801615754</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>朱*慶</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026/01/13</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>26011343534591</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>x200129</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>67</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1005</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/01/15&lt;br&gt;01/15 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>M51801615754</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>朱*慶</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026/01/10</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>26011043215466</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>全家取貨付款</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>superart</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>S ➜建議50-55KG</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>HME03001-BK-S</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>67</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>全家取貨付款</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>30</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>365</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/01/27&lt;br&gt;01/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>16327964981</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>邱*慶</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/露天.xlsx
+++ b/data/露天.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Z34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1293,6 +1293,2778 @@
         </is>
       </c>
       <c r="Z8" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026/02/26</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>26022648358294</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>a0960968836</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>藏藍色</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>HME03001-DN-L</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>67</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>65</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>199</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/05&lt;br&gt;03/04 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>P08209345224</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>劉*廷</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0960******</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>泰樂門市||台北市內湖區安泰街26號28號||N||0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026/02/26</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>26022648358294</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>a0960968836</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>67</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>65</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>199</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/05&lt;br&gt;03/04 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>P08209345224</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>劉*廷</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0960******</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>泰樂門市||台北市內湖區安泰街26號28號||N||0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026/02/26</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>26022648266686</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>yenny</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>22021591654333</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>【白色】吊帶款▶中長版 ❗️微透❗️</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>134</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>55</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>323</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>03/01 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>26EQD20106070</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>李***生</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0926******</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4789||萊爾富八德陂塘店||桃園市八德區高城路６６號、高城六街２號</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026/02/26</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>26022648266686</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>yenny</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>22021591654333</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>【白色】吊帶款▶加長版 ❗️微透❗️</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>134</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>55</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>323</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>03/01 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>26EQD20106070</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>李***生</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0926******</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4789||萊爾富八德陂塘店||桃園市八德區高城路６６號、高城六街２號</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026/02/24</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>26022448136964</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>x26216360</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>67</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>55</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>390</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>02/28 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>26EQD21146135</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>林*勝</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>0903******</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4658||萊爾富淡水英才店||新北市淡水區清水街２號、英專路４３號</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026/02/23</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>26022347876463</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>beat966977</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M14" t="n">
+        <v>67</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>65</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>333</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>02/26 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>N91717374695</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>李*志</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>26022147748383</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>cvs3065678</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>67</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>55</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>323</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>02/26 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>26END31355801</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>吳*賢</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>26022147703801</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>smtfrank</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>HME03001-PB-M</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>67</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>670</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>:)</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>02/25 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>N91711381433</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>游*忠</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>26022147703801</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>smtfrank</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>67</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>670</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>:)</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>02/25 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>N91711381433</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>游*忠</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>26022147703801</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>smtfrank</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>灰色</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>HME03001-GY-M</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>67</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>670</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>:)</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>02/25 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>N91711381433</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>游*忠</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>26022147703801</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>smtfrank</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>藏藍色</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>HME03001-DN-M</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M19" t="n">
+        <v>67</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>670</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>:)</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>02/25 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>N91711381433</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>游*忠</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>67</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>65</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>400</v>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>藏藍色</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>HME03001-DN-L</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>67</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>65</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>400</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>67</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>65</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>400</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>白色</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>HME03001-WH-L</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>67</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>65</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>400</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>咖啡色</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>HME03001-BR-L</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>67</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>65</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>400</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>HME03001-PB-XL</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>67</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>100</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>703</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>咖啡色</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>HME03001-BR-XL</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>67</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>100</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>703</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>酒紅色</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>HME03001-RD-XL</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>67</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>100</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>703</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>藏藍色</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>HME03001-DN-XL</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>67</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>100</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>703</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>紫色</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>HME03001-PU-XL</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>67</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>100</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>703</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>灰色</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>HME03001-GY-XL</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>67</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>100</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>703</v>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>白色</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>HME03001-WH-XL</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>3</v>
+      </c>
+      <c r="M31" t="n">
+        <v>67</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>100</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>703</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>22447281456959</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>白色｜高領</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>HFA02001-WH_TN-L</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>155</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>352</v>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>22447281456959</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>白色｜圓領</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>HFA02001-WH_CN-L</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>155</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>352</v>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>22031995614204</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>超舒適零觸感❄夏季涼爽高彈力純棉中腰無痕冰絲三角褲｜高彈力材料｜通過SGS認證｜內褲｜三角內褲｜女士內褲｜台灣現貨</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>白色</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>HFE03001-WH-L</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>42</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>352</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
         <is>
           <t>**********</t>
         </is>

--- a/data/露天.xlsx
+++ b/data/露天.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:Z27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,6 +557,2778 @@
       <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>收件地址</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026/02/26</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>26022648358294</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>a0960968836</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>藏藍色</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>HME03001-DN-L</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>67</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>65</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>199</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/05&lt;br&gt;03/04 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>P08209345224</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>劉*廷</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0960******</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>泰樂門市||台北市內湖區安泰街26號28號||N||0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026/02/26</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>26022648358294</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>a0960968836</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>67</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>65</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>199</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/05&lt;br&gt;03/04 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>P08209345224</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>劉*廷</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0960******</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>泰樂門市||台北市內湖區安泰街26號28號||N||0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026/02/26</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>26022648266686</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>yenny</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>22021591654333</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>【白色】吊帶款▶中長版 ❗️微透❗️</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>134</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>55</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>323</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>03/01 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>26EQD20106070</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>李***生</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0926******</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4789||萊爾富八德陂塘店||桃園市八德區高城路６６號、高城六街２號</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026/02/26</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>26022648266686</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>yenny</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>22021591654333</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>【白色】吊帶款▶加長版 ❗️微透❗️</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>134</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>55</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>323</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>03/01 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>26EQD20106070</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>李***生</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0926******</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4789||萊爾富八德陂塘店||桃園市八德區高城路６６號、高城六街２號</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026/02/24</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>26022448136964</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>x26216360</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>67</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>55</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>390</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>02/28 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>26EQD21146135</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>林*勝</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0903******</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4658||萊爾富淡水英才店||新北市淡水區清水街２號、英專路４３號</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026/02/23</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>26022347876463</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>beat966977</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M7" t="n">
+        <v>67</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>65</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>333</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>02/26 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>N91717374695</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>李*志</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>26022147748383</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>cvs3065678</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>67</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>55</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>323</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>02/26 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>26END31355801</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>吳*賢</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>26022147703801</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>smtfrank</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>HME03001-PB-M</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>67</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>670</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>:)</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>02/25 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>N91711381433</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>游*忠</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>26022147703801</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>smtfrank</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>67</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>670</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>:)</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>02/25 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>N91711381433</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>游*忠</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>26022147703801</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>smtfrank</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>灰色</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>HME03001-GY-M</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>67</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>670</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>:)</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>02/25 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>N91711381433</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>游*忠</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>26022147703801</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>smtfrank</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>藏藍色</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>HME03001-DN-M</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" t="n">
+        <v>67</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>670</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>:)</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>02/25 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>N91711381433</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>游*忠</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>67</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>65</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>400</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>藏藍色</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>HME03001-DN-L</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>67</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>65</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>400</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>67</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>65</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>400</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>白色</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>HME03001-WH-L</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>67</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>65</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>400</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>咖啡色</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>HME03001-BR-L</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>67</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>65</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>400</v>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>HME03001-PB-XL</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>67</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>100</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>703</v>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>咖啡色</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>HME03001-BR-XL</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>67</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>100</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>703</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>酒紅色</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>HME03001-RD-XL</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>67</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>100</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>703</v>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>藏藍色</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>HME03001-DN-XL</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>67</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>100</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>703</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>紫色</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>HME03001-PU-XL</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>67</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>100</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>703</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>灰色</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>HME03001-GY-XL</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>67</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>100</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>703</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>白色</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>HME03001-WH-XL</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>3</v>
+      </c>
+      <c r="M24" t="n">
+        <v>67</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>100</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>703</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>22447281456959</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>白色｜高領</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>HFA02001-TN-WH-L</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>155</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>352</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>22447281456959</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>白色｜圓領</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>HFA02001-CN-WH-L</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>155</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>352</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>22031995614204</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>超舒適零觸感❄夏季涼爽高彈力純棉中腰無痕冰絲三角褲｜高彈力材料｜通過SGS認證｜內褲｜三角內褲｜女士內褲｜台灣現貨</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>白色</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>HFE03001-WH-L</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>42</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>352</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>**********</t>
         </is>
       </c>
     </row>

--- a/data/露天.xlsx
+++ b/data/露天.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z27"/>
+  <dimension ref="A1:Z31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3331,6 +3331,204 @@
           <t>**********</t>
         </is>
       </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025/06/25</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>25062521046189</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>akk238</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>S ➜建議50-55KG</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>HME03001-BK-S</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>5</v>
+      </c>
+      <c r="M28" t="n">
+        <v>67</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>65</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>400</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2025/07/09&lt;br&gt;07/08 已領取退貨</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>E57180550168</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>高*華</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>買家未取貨，日報表需列出，未取貨/退貨運費 視該筆訂單（D_付款方式）選擇的超商方式計入費用；不扣庫存，不計入出庫</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>7-11取貨$60／全家取貨$60／OK超商取貨$60／萊爾富取貨$50／中華郵政$65（中華郵政部份是否能設定手KEY）</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/露天.xlsx
+++ b/data/露天.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Z34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1293,6 +1293,2778 @@
         </is>
       </c>
       <c r="Z8" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026/02/26</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>26022648358294</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>a0960968836</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>藏藍色</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>HME03001-DN-L</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>67</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>65</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>199</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/05&lt;br&gt;03/04 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>P08209345224</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>劉*廷</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0960******</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>泰樂門市||台北市內湖區安泰街26號28號||N||0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026/02/26</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>26022648358294</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>a0960968836</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>67</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>65</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>199</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/05&lt;br&gt;03/04 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>P08209345224</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>劉*廷</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0960******</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>泰樂門市||台北市內湖區安泰街26號28號||N||0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026/02/26</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>26022648266686</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>yenny</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>22021591654333</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>【白色】吊帶款▶中長版 ❗️微透❗️</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>134</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>55</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>323</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>03/01 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>26EQD20106070</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>李***生</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0926******</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4789||萊爾富八德陂塘店||桃園市八德區高城路６６號、高城六街２號</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026/02/26</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>26022648266686</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>yenny</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>22021591654333</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>【白色】吊帶款▶加長版 ❗️微透❗️</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>134</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>55</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>323</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>03/01 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>26EQD20106070</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>李***生</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0926******</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4789||萊爾富八德陂塘店||桃園市八德區高城路６６號、高城六街２號</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026/02/24</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>26022448136964</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>x26216360</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>67</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>55</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>390</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>02/28 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>26EQD21146135</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>林*勝</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>0903******</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4658||萊爾富淡水英才店||新北市淡水區清水街２號、英專路４３號</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026/02/23</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>26022347876463</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>beat966977</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M14" t="n">
+        <v>67</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>65</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>333</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>02/26 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>N91717374695</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>李*志</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>26022147748383</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>cvs3065678</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>67</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>55</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>323</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>02/26 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>26END31355801</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>吳*賢</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>26022147703801</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>smtfrank</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>HME03001-PB-M</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>67</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>670</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>:)</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>02/25 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>N91711381433</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>游*忠</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>26022147703801</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>smtfrank</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>67</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>670</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>:)</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>02/25 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>N91711381433</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>游*忠</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>26022147703801</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>smtfrank</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>灰色</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>HME03001-GY-M</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>67</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>670</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>:)</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>02/25 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>N91711381433</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>游*忠</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>26022147703801</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>smtfrank</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>藏藍色</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>HME03001-DN-M</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M19" t="n">
+        <v>67</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>670</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>:)</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>02/25 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>N91711381433</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>游*忠</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>67</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>65</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>400</v>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>藏藍色</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>HME03001-DN-L</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>67</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>65</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>400</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>67</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>65</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>400</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>白色</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>HME03001-WH-L</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>67</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>65</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>400</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>咖啡色</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>HME03001-BR-L</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>67</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>65</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>400</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>HME03001-PB-XL</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>67</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>100</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>703</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>咖啡色</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>HME03001-BR-XL</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>67</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>100</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>703</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>酒紅色</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>HME03001-RD-XL</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>67</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>100</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>703</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>藏藍色</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>HME03001-DN-XL</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>67</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>100</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>703</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>紫色</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>HME03001-PU-XL</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>67</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>100</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>703</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>灰色</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>HME03001-GY-XL</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>67</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>100</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>703</v>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>白色</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>HME03001-WH-XL</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>3</v>
+      </c>
+      <c r="M31" t="n">
+        <v>67</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>100</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>703</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>22447281456959</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>白色｜高領</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>HFA02001-TN-WH-L</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>155</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>352</v>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>22447281456959</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>白色｜圓領</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>HFA02001-CN-WH-L</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>155</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>352</v>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>22031995614204</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>超舒適零觸感❄夏季涼爽高彈力純棉中腰無痕冰絲三角褲｜高彈力材料｜通過SGS認證｜內褲｜三角內褲｜女士內褲｜台灣現貨</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>白色</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>HFE03001-WH-L</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>42</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>352</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
         <is>
           <t>**********</t>
         </is>

--- a/data/露天.xlsx
+++ b/data/露天.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,6 +557,744 @@
       <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>收件地址</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026/01/20</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>26012044321148</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>jimshue</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>22212317280954</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>『單顆入』好評銷售冠軍👑台灣天然養生手工黑糖塊｜老薑紅棗桂圓海燕窩｜冬日暖身｜生理期保養｜暖男送女友必備🎁｜黑糖磚</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>老薑黑糖塊</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>YGJ03002-OG</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>17</v>
+      </c>
+      <c r="S2" t="n">
+        <v>83</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/01/26&lt;br&gt;01/24 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>26DME37477238</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>許*誠</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026/01/13</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>26011343534591</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>x200129</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>67</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1005</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/01/15&lt;br&gt;01/15 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>M51801615754</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>朱*慶</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026/01/13</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>26011343534591</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>x200129</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>咖啡色</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>HME03001-BR-L</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>67</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1005</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/01/15&lt;br&gt;01/15 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>M51801615754</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>朱*慶</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026/01/13</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>26011343534591</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>x200129</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>灰色</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>HME03001-GY-L</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>67</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1005</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/01/15&lt;br&gt;01/15 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>M51801615754</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>朱*慶</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026/01/13</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>26011343534591</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>x200129</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>酒紅色</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>HME03001-RD-L</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>67</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1005</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/01/15&lt;br&gt;01/15 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>M51801615754</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>朱*慶</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026/01/13</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>26011343534591</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>x200129</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>67</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1005</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/01/15&lt;br&gt;01/15 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>M51801615754</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>朱*慶</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026/01/10</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>26011043215466</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>全家取貨付款</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>superart</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>S ➜建議50-55KG</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>HME03001-BK-S</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>67</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>全家取貨付款</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>30</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>365</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/01/27&lt;br&gt;01/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>16327964981</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>邱*慶</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>**********</t>
         </is>
       </c>
     </row>

--- a/data/露天.xlsx
+++ b/data/露天.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -545,6 +545,744 @@
       <c r="Z1" t="inlineStr">
         <is>
           <t>收件地址</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026/01/20</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>26012044321148</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>jimshue</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>22212317280954</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>『單顆入』好評銷售冠軍👑台灣天然養生手工黑糖塊｜老薑紅棗桂圓海燕窩｜冬日暖身｜生理期保養｜暖男送女友必備🎁｜黑糖磚</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>老薑黑糖塊</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>YGJ03002-OG</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>17</v>
+      </c>
+      <c r="S2" t="n">
+        <v>83</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/01/26&lt;br&gt;01/24 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>26DME37477238</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>許*誠</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026/01/13</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>26011343534591</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>x200129</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>67</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1005</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/01/15&lt;br&gt;01/15 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>M51801615754</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>朱*慶</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026/01/13</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>26011343534591</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>x200129</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>咖啡色</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>HME03001-BR-L</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>67</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1005</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/01/15&lt;br&gt;01/15 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>M51801615754</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>朱*慶</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026/01/13</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>26011343534591</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>x200129</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>灰色</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>HME03001-GY-L</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>67</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1005</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/01/15&lt;br&gt;01/15 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>M51801615754</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>朱*慶</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026/01/13</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>26011343534591</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>x200129</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>酒紅色</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>HME03001-RD-L</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>67</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1005</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/01/15&lt;br&gt;01/15 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>M51801615754</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>朱*慶</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026/01/13</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>26011343534591</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>x200129</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>67</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1005</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/01/15&lt;br&gt;01/15 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>M51801615754</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>朱*慶</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026/01/10</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>26011043215466</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>全家取貨付款</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>superart</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>S ➜建議50-55KG</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>HME03001-BK-S</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>67</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>全家取貨付款</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>30</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>365</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/01/27&lt;br&gt;01/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>16327964981</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>邱*慶</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>**********</t>
         </is>
       </c>
     </row>

--- a/data/露天.xlsx
+++ b/data/露天.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Z34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1281,6 +1281,2798 @@
         </is>
       </c>
       <c r="Z8" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026/02/26</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>26022648358294</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>a0960968836</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>藏藍色</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>HME03001-DN-L</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>67</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>65</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>199</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/05&lt;br&gt;03/04 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>P08209345224</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>劉*廷</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026/02/26</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>26022648358294</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>a0960968836</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>67</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>65</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>199</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/05&lt;br&gt;03/04 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>P08209345224</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>劉*廷</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026/02/26</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>26022648266686</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>yenny</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>22021591654333</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>【白色】吊帶款▶中長版 ❗️微透❗️</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>134</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>55</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>323</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/16&lt;br&gt;03/01 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>26EQD20106070</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>李***生</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026/02/26</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>26022648266686</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>yenny</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>22021591654333</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>【白色】吊帶款▶加長版 ❗️微透❗️</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>134</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>55</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>323</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/16&lt;br&gt;03/01 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>26EQD20106070</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>李***生</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026/02/24</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>26022448136964</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>x26216360</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>67</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>55</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>390</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/15&lt;br&gt;02/28 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>26EQD21146135</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>林*勝</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026/02/23</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>26022347876463</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>beat966977</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M14" t="n">
+        <v>67</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>65</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>333</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/13&lt;br&gt;02/26 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>N91717374695</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>李*志</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>26022147748383</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>cvs3065678</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>67</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>55</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>323</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/13&lt;br&gt;02/26 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>26END31355801</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>吳*賢</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>26022147703801</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>smtfrank</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>HME03001-PB-M</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>67</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>670</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>:)</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/12&lt;br&gt;02/25 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>N91711381433</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>游*忠</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>26022147703801</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>smtfrank</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>67</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>670</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>:)</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/12&lt;br&gt;02/25 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>N91711381433</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>游*忠</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>26022147703801</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>smtfrank</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>灰色</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>HME03001-GY-M</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>67</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>670</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>:)</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/12&lt;br&gt;02/25 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>N91711381433</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>游*忠</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>26022147703801</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>smtfrank</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>藏藍色</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>HME03001-DN-M</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M19" t="n">
+        <v>67</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>670</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>:)</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/12&lt;br&gt;02/25 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>N91711381433</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>游*忠</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>67</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>65</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>400</v>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>藏藍色</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>HME03001-DN-L</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>67</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>65</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>400</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>67</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>65</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>400</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>白色</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>HME03001-WH-L</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>67</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>65</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>400</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>咖啡色</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>HME03001-BR-L</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>67</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>65</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>400</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>HME03001-PB-XL</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>67</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>100</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>703</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>咖啡色</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>HME03001-BR-XL</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>67</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>100</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>703</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>酒紅色</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>HME03001-RD-XL</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>67</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>100</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>703</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>藏藍色</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>HME03001-DN-XL</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>67</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>100</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>703</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>紫色</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>HME03001-PU-XL</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>67</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>100</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>703</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>灰色</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>HME03001-GY-XL</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>67</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>100</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>703</v>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>白色</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>HME03001-WH-XL</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>3</v>
+      </c>
+      <c r="M31" t="n">
+        <v>67</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>100</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>703</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>22447281456959</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>白色｜高領</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>HFA02001-WH_TN-L</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>155</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>352</v>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>22447281456959</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>白色｜圓領</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>HFA02001-WH_CN-L</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>155</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>352</v>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>22031995614204</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>超舒適零觸感❄夏季涼爽高彈力純棉中腰無痕冰絲三角褲｜高彈力材料｜通過SGS認證｜內褲｜三角內褲｜女士內褲｜台灣現貨</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>白色</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>HFE03001-WH-L</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>42</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>352</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
         <is>
           <t>**********</t>
         </is>

--- a/data/露天.xlsx
+++ b/data/露天.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z34"/>
+  <dimension ref="A1:Z38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26022648358294</v>
+        <v>26022648266686</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1302,47 +1302,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7-11取貨付款</t>
+          <t>萊爾富取貨付款</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>a0960968836</t>
+          <t>yenny</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>21828333346889</v>
+        <v>22021591654333</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>藏藍色</t>
+          <t>【白色】吊帶款▶中長版 ❗️微透❗️</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>L ➜建議70-75KG</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>HME03001-DN-L</t>
-        </is>
-      </c>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>7-11取貨付款</t>
+          <t>萊爾富取貨付款</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1352,28 +1348,28 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>199</v>
+        <v>323</v>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>訂單完成&lt;br&gt;2026/03/05&lt;br&gt;03/04 買家已取貨</t>
+          <t>訂單完成&lt;br&gt;2026/03/16&lt;br&gt;03/01 買家已取貨</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>P08209345224</t>
+          <t>26EQD20106070</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>劉*廷</t>
+          <t>李***生</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1399,7 +1395,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26022648358294</v>
+        <v>26022648266686</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1408,47 +1404,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7-11取貨付款</t>
+          <t>萊爾富取貨付款</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>a0960968836</t>
+          <t>yenny</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>21828333346889</v>
+        <v>22021591654333</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>黑色</t>
+          <t>【白色】吊帶款▶加長版 ❗️微透❗️</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>L ➜建議70-75KG</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>HME03001-BK-L</t>
-        </is>
-      </c>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>7-11取貨付款</t>
+          <t>萊爾富取貨付款</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -1458,28 +1450,28 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>199</v>
+        <v>323</v>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>訂單完成&lt;br&gt;2026/03/05&lt;br&gt;03/04 買家已取貨</t>
+          <t>訂單完成&lt;br&gt;2026/03/16&lt;br&gt;03/01 買家已取貨</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>P08209345224</t>
+          <t>26EQD20106070</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>劉*廷</t>
+          <t>李***生</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1501,11 +1493,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026/02/26</t>
+          <t>2026/02/03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26022648266686</v>
+        <v>26020345883124</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1514,26 +1506,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>萊爾富取貨付款</t>
+          <t>7-11取貨付款</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>yenny</t>
+          <t>kuzzar</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>22021591654333</v>
+        <v>22447281456959</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨</t>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>【白色】吊帶款▶中長版 ❗️微透❗️</t>
+          <t>白色｜高領</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1541,16 +1533,20 @@
           <t>L</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>HFA02001-WH_TN-L</t>
+        </is>
+      </c>
       <c r="L11" t="n">
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>萊爾富取貨付款</t>
+          <t>7-11取貨付款</t>
         </is>
       </c>
       <c r="O11" t="n">
@@ -1560,28 +1556,28 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>323</v>
+        <v>352</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>訂單完成&lt;br&gt;2026/03/16&lt;br&gt;03/01 買家已取貨</t>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>26EQD20106070</t>
+          <t>N33024165187</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>李***生</t>
+          <t>楊*賓</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -1603,11 +1599,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026/02/26</t>
+          <t>2026/02/03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26022648266686</v>
+        <v>26020345883124</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1616,26 +1612,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>萊爾富取貨付款</t>
+          <t>7-11取貨付款</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>yenny</t>
+          <t>kuzzar</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>22021591654333</v>
+        <v>22447281456959</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨</t>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>【白色】吊帶款▶加長版 ❗️微透❗️</t>
+          <t>白色｜圓領</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1643,16 +1639,20 @@
           <t>L</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>HFA02001-WH_CN-L</t>
+        </is>
+      </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>萊爾富取貨付款</t>
+          <t>7-11取貨付款</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -1662,28 +1662,28 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>323</v>
+        <v>352</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>訂單完成&lt;br&gt;2026/03/16&lt;br&gt;03/01 買家已取貨</t>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>26EQD20106070</t>
+          <t>N33024165187</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>李***生</t>
+          <t>楊*賓</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -1705,11 +1705,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026/02/24</t>
+          <t>2026/02/26</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26022448136964</v>
+        <v>26022648358294</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>萊爾富取貨付款</t>
+          <t>7-11取貨付款</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>x26216360</t>
+          <t>a0960968836</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1737,28 +1737,28 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>黑色</t>
+          <t>藏藍色</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>M ➜建議60-65KG</t>
+          <t>L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>HME03001-BK-M</t>
+          <t>HME03001-DN-L</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>67</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>萊爾富取貨付款</t>
+          <t>7-11取貨付款</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -1768,28 +1768,28 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>390</v>
+        <v>199</v>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>訂單完成&lt;br&gt;2026/03/15&lt;br&gt;02/28 買家已取貨</t>
+          <t>訂單完成&lt;br&gt;2026/03/05&lt;br&gt;03/04 買家已取貨</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>26EQD21146135</t>
+          <t>P08209345224</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>林*勝</t>
+          <t>劉*廷</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -1811,11 +1811,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026/02/23</t>
+          <t>2026/02/26</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26022347876463</v>
+        <v>26022648358294</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>beat966977</t>
+          <t>a0960968836</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>寶藍色</t>
+          <t>黑色</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1853,11 +1853,11 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>HME03001-PB-L</t>
+          <t>HME03001-BK-L</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>67</v>
@@ -1880,22 +1880,22 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>333</v>
+        <v>199</v>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>訂單完成&lt;br&gt;2026/03/13&lt;br&gt;02/26 買家已取貨</t>
+          <t>訂單完成&lt;br&gt;2026/03/05&lt;br&gt;03/04 買家已取貨</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>N91717374695</t>
+          <t>P08209345224</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>李*志</t>
+          <t>劉*廷</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -1917,11 +1917,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026/02/21</t>
+          <t>2026/02/26</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26022147748383</v>
+        <v>26022648266686</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,37 +1936,37 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>cvs3065678</t>
+          <t>yenny</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>21828333346889</v>
+        <v>22021591654333</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>黑色</t>
+          <t>【白色】吊帶款▶中長版 ❗️微透❗️</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>L ➜建議70-75KG</t>
+          <t>L</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>HME03001-BK-L</t>
+          <t>HFC01001-TS-MD-WH-L</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1991,17 +1991,17 @@
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>訂單完成&lt;br&gt;2026/03/13&lt;br&gt;02/26 買家已取貨</t>
+          <t>訂單完成&lt;br&gt;2026/03/16&lt;br&gt;03/01 買家已取貨</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>26END31355801</t>
+          <t>26EQD20106070</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>吳*賢</t>
+          <t>李***生</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2023,11 +2023,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026/02/21</t>
+          <t>2026/02/26</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>26022147703801</v>
+        <v>26022648266686</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2036,47 +2036,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7-11取貨付款</t>
+          <t>萊爾富取貨付款</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>smtfrank</t>
+          <t>yenny</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>21828333346889</v>
+        <v>22021591654333</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>寶藍色</t>
+          <t>【白色】吊帶款▶加長版 ❗️微透❗️</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>M ➜建議60-65KG</t>
+          <t>L</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>HME03001-PB-M</t>
+          <t>HFC01001-TS-LG-WH-L</t>
         </is>
       </c>
       <c r="L16" t="n">
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>7-11取貨付款</t>
+          <t>萊爾富取貨付款</t>
         </is>
       </c>
       <c r="O16" t="n">
@@ -2086,32 +2086,28 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>670</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>:)</t>
-        </is>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>訂單完成&lt;br&gt;2026/03/12&lt;br&gt;02/25 買家已取貨</t>
+          <t>訂單完成&lt;br&gt;2026/03/16&lt;br&gt;03/01 買家已取貨</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>N91711381433</t>
+          <t>26EQD20106070</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>游*忠</t>
+          <t>李***生</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -2133,11 +2129,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026/02/21</t>
+          <t>2026/02/24</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26022147703801</v>
+        <v>26022448136964</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2146,13 +2142,13 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7-11取貨付款</t>
+          <t>萊爾富取貨付款</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>smtfrank</t>
+          <t>x26216360</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2179,14 +2175,14 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M17" t="n">
         <v>67</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>7-11取貨付款</t>
+          <t>萊爾富取貨付款</t>
         </is>
       </c>
       <c r="O17" t="n">
@@ -2196,32 +2192,28 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>670</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>:)</t>
-        </is>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>訂單完成&lt;br&gt;2026/03/12&lt;br&gt;02/25 買家已取貨</t>
+          <t>訂單完成&lt;br&gt;2026/03/15&lt;br&gt;02/28 買家已取貨</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>N91711381433</t>
+          <t>26EQD21146135</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>游*忠</t>
+          <t>林*勝</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -2243,11 +2235,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026/02/21</t>
+          <t>2026/02/23</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26022147703801</v>
+        <v>26022347876463</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2262,7 +2254,7 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>smtfrank</t>
+          <t>beat966977</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2275,21 +2267,21 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>灰色</t>
+          <t>寶藍色</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>M ➜建議60-65KG</t>
+          <t>L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>HME03001-GY-M</t>
+          <t>HME03001-PB-L</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
         <v>67</v>
@@ -2306,32 +2298,28 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>670</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>:)</t>
-        </is>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>訂單完成&lt;br&gt;2026/03/12&lt;br&gt;02/25 買家已取貨</t>
+          <t>訂單完成&lt;br&gt;2026/03/13&lt;br&gt;02/26 買家已取貨</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>N91711381433</t>
+          <t>N91717374695</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>游*忠</t>
+          <t>李*志</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -2357,7 +2345,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26022147703801</v>
+        <v>26022147748383</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2366,13 +2354,13 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7-11取貨付款</t>
+          <t>萊爾富取貨付款</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>smtfrank</t>
+          <t>cvs3065678</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2385,28 +2373,28 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>藏藍色</t>
+          <t>黑色</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>M ➜建議60-65KG</t>
+          <t>L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>HME03001-DN-M</t>
+          <t>HME03001-BK-L</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M19" t="n">
         <v>67</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>7-11取貨付款</t>
+          <t>萊爾富取貨付款</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -2416,32 +2404,28 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>670</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>:)</t>
-        </is>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>訂單完成&lt;br&gt;2026/03/12&lt;br&gt;02/25 買家已取貨</t>
+          <t>訂單完成&lt;br&gt;2026/03/13&lt;br&gt;02/26 買家已取貨</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>N91711381433</t>
+          <t>26END31355801</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>游*忠</t>
+          <t>吳*賢</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -2463,11 +2447,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026/02/09</t>
+          <t>2026/02/21</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>26020946668756</v>
+        <v>26022147703801</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2482,7 +2466,7 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>post004100</t>
+          <t>smtfrank</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2500,12 +2484,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>L ➜建議70-75KG</t>
+          <t>M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>HME03001-PB-L</t>
+          <t>HME03001-PB-M</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -2526,28 +2510,32 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>400</v>
-      </c>
-      <c r="T20" t="inlineStr"/>
+        <v>670</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>:)</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+          <t>訂單完成&lt;br&gt;2026/03/12&lt;br&gt;02/25 買家已取貨</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>N59688810691</t>
+          <t>N91711381433</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>鄧*誌</t>
+          <t>游*忠</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -2569,11 +2557,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026/02/09</t>
+          <t>2026/02/21</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>26020946668756</v>
+        <v>26022147703801</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2588,7 +2576,7 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>post004100</t>
+          <t>smtfrank</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2601,21 +2589,21 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>藏藍色</t>
+          <t>黑色</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>L ➜建議70-75KG</t>
+          <t>M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>HME03001-DN-L</t>
+          <t>HME03001-BK-M</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M21" t="n">
         <v>67</v>
@@ -2632,28 +2620,32 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>400</v>
-      </c>
-      <c r="T21" t="inlineStr"/>
+        <v>670</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>:)</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+          <t>訂單完成&lt;br&gt;2026/03/12&lt;br&gt;02/25 買家已取貨</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>N59688810691</t>
+          <t>N91711381433</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>鄧*誌</t>
+          <t>游*忠</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -2675,11 +2667,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026/02/09</t>
+          <t>2026/02/21</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>26020946668756</v>
+        <v>26022147703801</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2694,7 +2686,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>post004100</t>
+          <t>smtfrank</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -2707,21 +2699,21 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>黑色</t>
+          <t>灰色</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>L ➜建議70-75KG</t>
+          <t>M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>HME03001-BK-L</t>
+          <t>HME03001-GY-M</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M22" t="n">
         <v>67</v>
@@ -2738,28 +2730,32 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>400</v>
-      </c>
-      <c r="T22" t="inlineStr"/>
+        <v>670</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>:)</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+          <t>訂單完成&lt;br&gt;2026/03/12&lt;br&gt;02/25 買家已取貨</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>N59688810691</t>
+          <t>N91711381433</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>鄧*誌</t>
+          <t>游*忠</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -2781,11 +2777,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026/02/09</t>
+          <t>2026/02/21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>26020946668756</v>
+        <v>26022147703801</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2800,7 +2796,7 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>post004100</t>
+          <t>smtfrank</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2813,21 +2809,21 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>白色</t>
+          <t>藏藍色</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>L ➜建議70-75KG</t>
+          <t>M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>HME03001-WH-L</t>
+          <t>HME03001-DN-M</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M23" t="n">
         <v>67</v>
@@ -2844,28 +2840,32 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>400</v>
-      </c>
-      <c r="T23" t="inlineStr"/>
+        <v>670</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>:)</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+          <t>訂單完成&lt;br&gt;2026/03/12&lt;br&gt;02/25 買家已取貨</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>N59688810691</t>
+          <t>N91711381433</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>鄧*誌</t>
+          <t>游*忠</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>咖啡色</t>
+          <t>寶藍色</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>HME03001-BR-L</t>
+          <t>HME03001-PB-L</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -2993,11 +2993,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026/02/07</t>
+          <t>2026/02/09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26020746340576</v>
+        <v>26020946668756</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3006,17 +3006,13 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PChomePay支付連 信用卡(一次付清)</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026/02/07</t>
-        </is>
-      </c>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>kf199172</t>
+          <t>post004100</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3029,17 +3025,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>寶藍色</t>
+          <t>藏藍色</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>XL ➜建議80-85KG</t>
+          <t>L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>HME03001-PB-XL</t>
+          <t>HME03001-DN-L</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3050,7 +3046,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>郵寄寄送</t>
+          <t>7-11取貨付款</t>
         </is>
       </c>
       <c r="O25" t="n">
@@ -3060,28 +3056,28 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>703</v>
+        <v>400</v>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>94699940004510637002</t>
+          <t>N59688810691</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>鍾長誠</t>
+          <t>鄧*誌</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -3103,11 +3099,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026/02/07</t>
+          <t>2026/02/09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>26020746340576</v>
+        <v>26020946668756</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3116,17 +3112,13 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PChomePay支付連 信用卡(一次付清)</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026/02/07</t>
-        </is>
-      </c>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>kf199172</t>
+          <t>post004100</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3139,17 +3131,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>咖啡色</t>
+          <t>黑色</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>XL ➜建議80-85KG</t>
+          <t>L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>HME03001-BR-XL</t>
+          <t>HME03001-BK-L</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -3160,7 +3152,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>郵寄寄送</t>
+          <t>7-11取貨付款</t>
         </is>
       </c>
       <c r="O26" t="n">
@@ -3170,28 +3162,28 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>703</v>
+        <v>400</v>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>94699940004510637002</t>
+          <t>N59688810691</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>鍾長誠</t>
+          <t>鄧*誌</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -3213,11 +3205,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026/02/07</t>
+          <t>2026/02/09</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26020746340576</v>
+        <v>26020946668756</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3226,17 +3218,13 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PChomePay支付連 信用卡(一次付清)</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026/02/07</t>
-        </is>
-      </c>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>kf199172</t>
+          <t>post004100</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3249,17 +3237,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>酒紅色</t>
+          <t>白色</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>XL ➜建議80-85KG</t>
+          <t>L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>HME03001-RD-XL</t>
+          <t>HME03001-WH-L</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -3270,7 +3258,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>郵寄寄送</t>
+          <t>7-11取貨付款</t>
         </is>
       </c>
       <c r="O27" t="n">
@@ -3280,28 +3268,28 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>703</v>
+        <v>400</v>
       </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>94699940004510637002</t>
+          <t>N59688810691</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>鍾長誠</t>
+          <t>鄧*誌</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -3323,11 +3311,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026/02/07</t>
+          <t>2026/02/09</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26020746340576</v>
+        <v>26020946668756</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3336,17 +3324,13 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>PChomePay支付連 信用卡(一次付清)</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026/02/07</t>
-        </is>
-      </c>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>kf199172</t>
+          <t>post004100</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3359,17 +3343,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>藏藍色</t>
+          <t>咖啡色</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>XL ➜建議80-85KG</t>
+          <t>L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>HME03001-DN-XL</t>
+          <t>HME03001-BR-L</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -3380,7 +3364,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>郵寄寄送</t>
+          <t>7-11取貨付款</t>
         </is>
       </c>
       <c r="O28" t="n">
@@ -3390,28 +3374,28 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>703</v>
+        <v>400</v>
       </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
-          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>94699940004510637002</t>
+          <t>N59688810691</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>鍾長誠</t>
+          <t>鄧*誌</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -3469,7 +3453,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>紫色</t>
+          <t>寶藍色</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3479,7 +3463,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>HME03001-PU-XL</t>
+          <t>HME03001-PB-XL</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -3579,7 +3563,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>灰色</t>
+          <t>咖啡色</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3589,7 +3573,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>HME03001-GY-XL</t>
+          <t>HME03001-BR-XL</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -3689,7 +3673,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>白色</t>
+          <t>酒紅色</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3699,11 +3683,11 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>HME03001-WH-XL</t>
+          <t>HME03001-RD-XL</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
         <v>67</v>
@@ -3763,11 +3747,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026/02/03</t>
+          <t>2026/02/07</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26020345883124</v>
+        <v>26020746340576</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3776,47 +3760,51 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7-11取貨付款</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>kuzzar</t>
+          <t>kf199172</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>22447281456959</v>
+        <v>21828333346889</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>白色｜高領</t>
+          <t>藏藍色</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>HFA02001-WH_TN-L</t>
+          <t>HME03001-DN-XL</t>
         </is>
       </c>
       <c r="L32" t="n">
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>155</v>
+        <v>67</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>7-11取貨付款</t>
+          <t>郵寄寄送</t>
         </is>
       </c>
       <c r="O32" t="n">
@@ -3826,28 +3814,28 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>352</v>
+        <v>703</v>
       </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
-          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>N33024165187</t>
+          <t>94699940004510637002</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>楊*賓</t>
+          <t>鍾長誠</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -3869,11 +3857,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026/02/03</t>
+          <t>2026/02/07</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>26020345883124</v>
+        <v>26020746340576</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3882,47 +3870,51 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>7-11取貨付款</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>kuzzar</t>
+          <t>kf199172</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>22447281456959</v>
+        <v>21828333346889</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>白色｜圓領</t>
+          <t>紫色</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>HFA02001-WH_CN-L</t>
+          <t>HME03001-PU-XL</t>
         </is>
       </c>
       <c r="L33" t="n">
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>155</v>
+        <v>67</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>7-11取貨付款</t>
+          <t>郵寄寄送</t>
         </is>
       </c>
       <c r="O33" t="n">
@@ -3932,28 +3924,28 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>352</v>
+        <v>703</v>
       </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
-          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>N33024165187</t>
+          <t>94699940004510637002</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>楊*賓</t>
+          <t>鍾長誠</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -3975,11 +3967,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026/02/03</t>
+          <t>2026/02/07</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26020345883124</v>
+        <v>26020746340576</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3988,47 +3980,51 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>7-11取貨付款</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>kuzzar</t>
+          <t>kf199172</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>22031995614204</v>
+        <v>21828333346889</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>超舒適零觸感❄夏季涼爽高彈力純棉中腰無痕冰絲三角褲｜高彈力材料｜通過SGS認證｜內褲｜三角內褲｜女士內褲｜台灣現貨</t>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>白色</t>
+          <t>灰色</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>HFE03001-WH-L</t>
+          <t>HME03001-GY-XL</t>
         </is>
       </c>
       <c r="L34" t="n">
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>7-11取貨付款</t>
+          <t>郵寄寄送</t>
         </is>
       </c>
       <c r="O34" t="n">
@@ -4038,41 +4034,469 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>352</v>
+        <v>703</v>
       </c>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>白色</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>HME03001-WH-XL</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>3</v>
+      </c>
+      <c r="M35" t="n">
+        <v>67</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>100</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>703</v>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>22447281456959</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>白色｜高領</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>HFA02001-TN-WH-L</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>155</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>352</v>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
           <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>N33024165187</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>楊*賓</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>**********</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>**********</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>22447281456959</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>白色｜圓領</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>HFA02001-CN-WH-L</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>155</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>352</v>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>22031995614204</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>超舒適零觸感❄夏季涼爽高彈力純棉中腰無痕冰絲三角褲｜高彈力材料｜通過SGS認證｜內褲｜三角內褲｜女士內褲｜台灣現貨</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>白色</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>HFE03001-WH-L</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" t="n">
+        <v>42</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>352</v>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
         <is>
           <t>**********</t>
         </is>

--- a/data/露天.xlsx
+++ b/data/露天.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Z34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1281,6 +1281,2806 @@
         </is>
       </c>
       <c r="Z8" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026/02/26</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>26022648358294</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>a0960968836</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>藏藍色</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>HME03001-DN-L</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>67</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>65</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>199</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/05&lt;br&gt;03/04 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>P08209345224</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>劉*廷</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026/02/26</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>26022648358294</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>a0960968836</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>67</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>65</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>199</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/05&lt;br&gt;03/04 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>P08209345224</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>劉*廷</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026/02/26</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>26022648266686</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>yenny</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>22021591654333</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>【白色】吊帶款▶中長版 ❗️微透❗️</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>HFC01001-TS-MD-WH-L</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>134</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>55</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>323</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/16&lt;br&gt;03/01 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>26EQD20106070</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>李***生</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026/02/26</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>26022648266686</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>yenny</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>22021591654333</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>【白色】吊帶款▶加長版 ❗️微透❗️</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>HFC01001-TS-LG-WH-L</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>134</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>55</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>323</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/16&lt;br&gt;03/01 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>26EQD20106070</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>李***生</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026/02/24</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>26022448136964</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>x26216360</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>67</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>55</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>390</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/15&lt;br&gt;02/28 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>26EQD21146135</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>林*勝</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026/02/23</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>26022347876463</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>beat966977</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M14" t="n">
+        <v>67</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>65</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>333</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/13&lt;br&gt;02/26 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>N91717374695</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>李*志</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>26022147748383</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>cvs3065678</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>67</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>萊爾富取貨付款</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>55</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>323</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/13&lt;br&gt;02/26 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>26END31355801</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>吳*賢</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>26022147703801</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>smtfrank</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>HME03001-PB-M</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>67</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>670</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>:)</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/12&lt;br&gt;02/25 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>N91711381433</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>游*忠</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>26022147703801</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>smtfrank</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>67</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>670</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>:)</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/12&lt;br&gt;02/25 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>N91711381433</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>游*忠</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>26022147703801</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>smtfrank</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>灰色</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>HME03001-GY-M</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>67</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>670</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>:)</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/12&lt;br&gt;02/25 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>N91711381433</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>游*忠</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026/02/21</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>26022147703801</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>smtfrank</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>藏藍色</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>M ➜建議60-65KG</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>HME03001-DN-M</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M19" t="n">
+        <v>67</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>670</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>:)</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/12&lt;br&gt;02/25 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>N91711381433</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>游*忠</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>67</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>65</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>400</v>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>藏藍色</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>HME03001-DN-L</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>67</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>65</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>400</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>67</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>65</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>400</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>白色</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>HME03001-WH-L</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>67</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>65</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>400</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026/02/09</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>26020946668756</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>post004100</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>咖啡色</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>L ➜建議70-75KG</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>HME03001-BR-L</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>67</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>65</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>400</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/13&lt;br&gt;02/12 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>N59688810691</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>鄧*誌</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>寶藍色</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>HME03001-PB-XL</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>67</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>100</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>703</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>咖啡色</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>HME03001-BR-XL</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>67</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>100</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>703</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>酒紅色</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>HME03001-RD-XL</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>67</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>100</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>703</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>藏藍色</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>HME03001-DN-XL</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>67</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>100</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>703</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>紫色</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>HME03001-PU-XL</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>67</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>100</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>703</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>灰色</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>HME03001-GY-XL</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>67</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>100</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>703</v>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>26020746340576</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PChomePay支付連 信用卡(一次付清)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026/02/07</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>kf199172</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>21828333346889</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>[台灣冠軍🏆爆賣30萬件]冰絲內褲 男內褲 涼感內褲 男士內褲 平口褲</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>白色</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>HME03001-WH-XL</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>3</v>
+      </c>
+      <c r="M31" t="n">
+        <v>67</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>郵寄寄送</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>100</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>703</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/03/03&lt;br&gt;02/10通知已出貨&lt;br&gt;款項已撥款給您，請至支付連帳戶查看</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>94699940004510637002</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>鍾長誠</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>22447281456959</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>白色｜高領</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>HFA02001-TN-WH-L</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>155</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>352</v>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>22447281456959</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>新品限時優惠❇️秋冬萬用打底衣🍁柔軟高彈莫代爾內搭長袖上衣｜長袖T恤 圓領上衣 高領 翻領 長T 內搭衣 長袖TEE</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>白色｜圓領</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>HFA02001-CN-WH-L</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>155</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>352</v>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>26020345883124</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>已出貨</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>kuzzar</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>22031995614204</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>超舒適零觸感❄夏季涼爽高彈力純棉中腰無痕冰絲三角褲｜高彈力材料｜通過SGS認證｜內褲｜三角內褲｜女士內褲｜台灣現貨</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>白色</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>HFE03001-WH-L</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>42</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>7-11取貨付款</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>352</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>訂單完成&lt;br&gt;2026/02/21&lt;br&gt;02/06 買家已取貨</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>N33024165187</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>楊*賓</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>**********</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
         <is>
           <t>**********</t>
         </is>
